--- a/data/output/Timehistory_modal/1-1/响应统计结果.xlsx
+++ b/data/output/Timehistory_modal/1-1/响应统计结果.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyFiles\GitHub\corner-point-response\data\output\Timehistory_modal\1-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YJh\github\corner-point-response\data\output\Timehistory_modal\1-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFBF0E4-BD95-4386-823C-E2ECF886D1B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E07357A-F1D6-43F9-84F2-823A2CDE194F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,24 +17,11 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
   <si>
     <t>folder</t>
   </si>
@@ -135,9 +122,21 @@
     <t>图18(a)</t>
   </si>
   <si>
+    <t>1-1模型</t>
+  </si>
+  <si>
     <t>matlab</t>
   </si>
   <si>
+    <t>集中质量模型</t>
+  </si>
+  <si>
+    <t>SAP2000模型</t>
+  </si>
+  <si>
+    <t>偏差(%)</t>
+  </si>
+  <si>
     <t>角度</t>
   </si>
   <si>
@@ -148,26 +147,6 @@
   </si>
   <si>
     <t>A</t>
-  </si>
-  <si>
-    <t>SAP2000模型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>偏差(%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1-1模型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>集中质量模型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2-1模型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -231,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -239,6 +218,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -271,34 +251,23 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="zh-CN" altLang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
-        <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="zh-CN"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -314,9 +283,9 @@
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
+              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
-            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
@@ -328,34 +297,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>6.9900000000000004E-2</c:v>
+                  <c:v>6.9769999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.0080000000000003E-2</c:v>
+                  <c:v>6.9930000000000006E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.9830000000000001E-2</c:v>
+                  <c:v>5.9639999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.4500000000000002E-2</c:v>
+                  <c:v>6.4280000000000004E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.4369999999999988E-2</c:v>
+                  <c:v>5.4140000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.4820000000000001E-2</c:v>
+                  <c:v>5.4609999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.3469999999999997E-2</c:v>
+                  <c:v>5.33E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.9490000000000001E-2</c:v>
+                  <c:v>5.9360000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.9270000000000003E-2</c:v>
+                  <c:v>5.9159999999999997E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.7000000000000002E-2</c:v>
+                  <c:v>5.6919999999999998E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -363,7 +332,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7256-4B3B-A7D9-FC58BBE319D8}"/>
+              <c16:uniqueId val="{00000000-7352-4732-BA29-1230A069F592}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -375,9 +344,9 @@
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
+              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
-            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
@@ -389,34 +358,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.12667999999999999</c:v>
+                  <c:v>0.1265</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.14549000000000001</c:v>
+                  <c:v>0.14530999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.13292999999999999</c:v>
+                  <c:v>0.13275000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.11892999999999999</c:v>
+                  <c:v>0.11869</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.9890000000000007E-2</c:v>
+                  <c:v>9.9510000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.2049999999999998E-2</c:v>
+                  <c:v>8.181999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.2180000000000003E-2</c:v>
+                  <c:v>8.2019999999999996E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.331E-2</c:v>
+                  <c:v>7.3209999999999997E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.5759999999999999E-2</c:v>
+                  <c:v>6.5680000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.5420000000000006E-2</c:v>
+                  <c:v>6.5370000000000011E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -424,7 +393,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7256-4B3B-A7D9-FC58BBE319D8}"/>
+              <c16:uniqueId val="{00000001-7352-4732-BA29-1230A069F592}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -436,9 +405,9 @@
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
+              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
-            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
@@ -450,34 +419,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.12712999999999999</c:v>
+                  <c:v>0.12695000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.14571999999999999</c:v>
+                  <c:v>0.14552999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.13317999999999999</c:v>
+                  <c:v>0.13299</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.11909</c:v>
+                  <c:v>0.11885999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.9930000000000005E-2</c:v>
+                  <c:v>9.955E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>8.1939999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>8.2170000000000007E-2</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>8.233E-2</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.553E-2</c:v>
+                  <c:v>7.5400000000000009E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7.0830000000000004E-2</c:v>
+                  <c:v>7.0730000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.9419999999999996E-2</c:v>
+                  <c:v>6.9339999999999999E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -485,7 +454,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-7256-4B3B-A7D9-FC58BBE319D8}"/>
+              <c16:uniqueId val="{00000002-7352-4732-BA29-1230A069F592}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -520,16 +489,16 @@
                 <a:lumOff val="85000"/>
               </a:schemeClr>
             </a:solidFill>
+            <a:prstDash val="solid"/>
             <a:round/>
           </a:ln>
-          <a:effectLst/>
         </c:spPr>
         <c:txPr>
           <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -567,9 +536,9 @@
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
+              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
-            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -580,15 +549,15 @@
           <a:noFill/>
           <a:ln>
             <a:noFill/>
+            <a:prstDash val="solid"/>
           </a:ln>
-          <a:effectLst/>
         </c:spPr>
         <c:txPr>
           <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -607,13 +576,6 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
@@ -622,15 +584,15 @@
         <a:noFill/>
         <a:ln>
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
-        <a:effectLst/>
       </c:spPr>
       <c:txPr>
         <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -648,13 +610,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
@@ -668,582 +623,16 @@
           <a:lumOff val="85000"/>
         </a:schemeClr>
       </a:solidFill>
+      <a:prstDash val="solid"/>
       <a:round/>
     </a:ln>
-    <a:effectLst/>
   </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="zh-CN"/>
-    </a:p>
-  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1263,10 +652,10 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="图表 1">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B88BC3C7-11B6-9441-49C9-48E9093C2329}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1573,23 +962,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="33.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="33.25" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="33.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1657,7 +1046,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -1665,67 +1054,67 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>6.4579999999999999E-2</v>
+        <v>6.4510000000000012E-2</v>
       </c>
       <c r="D2">
-        <v>0.12019000000000001</v>
+        <v>0.12007</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.12019000000000001</v>
+        <v>0.12007</v>
       </c>
       <c r="G2">
-        <v>6.9900000000000004E-2</v>
+        <v>6.9769999999999999E-2</v>
       </c>
       <c r="H2">
-        <v>0.12667999999999999</v>
+        <v>0.1265</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0.12712999999999999</v>
+        <v>0.12695000000000001</v>
       </c>
       <c r="K2">
-        <v>6.9900000000000004E-2</v>
+        <v>6.9769999999999999E-2</v>
       </c>
       <c r="L2">
-        <v>0.11654</v>
+        <v>0.11637</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.11656999999999999</v>
+        <v>0.1164</v>
       </c>
       <c r="O2">
-        <v>6.4920000000000005E-2</v>
+        <v>6.473000000000001E-2</v>
       </c>
       <c r="P2">
-        <v>0.12667999999999999</v>
+        <v>0.1265</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0.12684000000000001</v>
+        <v>0.12665999999999999</v>
       </c>
       <c r="S2">
-        <v>6.4920000000000005E-2</v>
+        <v>6.473000000000001E-2</v>
       </c>
       <c r="T2">
-        <v>0.11654</v>
+        <v>0.11637</v>
       </c>
       <c r="U2">
         <v>0</v>
       </c>
       <c r="V2">
-        <v>0.11667</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0.11650000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1733,67 +1122,67 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>6.4649999999999999E-2</v>
+        <v>6.4549999999999996E-2</v>
       </c>
       <c r="D3">
-        <v>0.13833000000000001</v>
+        <v>0.13819000000000001</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.13835</v>
+        <v>0.13821</v>
       </c>
       <c r="G3">
-        <v>7.0080000000000003E-2</v>
+        <v>6.9930000000000006E-2</v>
       </c>
       <c r="H3">
-        <v>0.14549000000000001</v>
+        <v>0.14530999999999999</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0.14571999999999999</v>
+        <v>0.14552999999999999</v>
       </c>
       <c r="K3">
-        <v>7.0080000000000003E-2</v>
+        <v>6.9930000000000006E-2</v>
       </c>
       <c r="L3">
-        <v>0.13400000000000001</v>
+        <v>0.13381000000000001</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.13400999999999999</v>
+        <v>0.13381000000000001</v>
       </c>
       <c r="O3">
-        <v>6.5319999999999989E-2</v>
+        <v>6.5129999999999993E-2</v>
       </c>
       <c r="P3">
-        <v>0.14549000000000001</v>
+        <v>0.14530999999999999</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>0.14582000000000001</v>
+        <v>0.14563000000000001</v>
       </c>
       <c r="S3">
-        <v>6.5319999999999989E-2</v>
+        <v>6.5129999999999993E-2</v>
       </c>
       <c r="T3">
-        <v>0.13400000000000001</v>
+        <v>0.13381000000000001</v>
       </c>
       <c r="U3">
         <v>0</v>
       </c>
       <c r="V3">
-        <v>0.13428000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0.13408999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -1801,67 +1190,67 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>5.4429999999999999E-2</v>
+        <v>5.4309999999999997E-2</v>
       </c>
       <c r="D4">
-        <v>0.12642999999999999</v>
+        <v>0.12629000000000001</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.12645000000000001</v>
+        <v>0.1263</v>
       </c>
       <c r="G4">
-        <v>5.9830000000000001E-2</v>
+        <v>5.9639999999999999E-2</v>
       </c>
       <c r="H4">
-        <v>0.13292999999999999</v>
+        <v>0.13275000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0.13317999999999999</v>
+        <v>0.13299</v>
       </c>
       <c r="K4">
-        <v>5.9830000000000001E-2</v>
+        <v>5.9639999999999999E-2</v>
       </c>
       <c r="L4">
-        <v>0.12272</v>
+        <v>0.12252</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.12274</v>
+        <v>0.12254</v>
       </c>
       <c r="O4">
-        <v>5.5469999999999998E-2</v>
+        <v>5.525E-2</v>
       </c>
       <c r="P4">
-        <v>0.13292999999999999</v>
+        <v>0.13275000000000001</v>
       </c>
       <c r="Q4">
         <v>0</v>
       </c>
       <c r="R4">
-        <v>0.13320000000000001</v>
+        <v>0.13300999999999999</v>
       </c>
       <c r="S4">
-        <v>5.5469999999999998E-2</v>
+        <v>5.525E-2</v>
       </c>
       <c r="T4">
-        <v>0.12272</v>
+        <v>0.12252</v>
       </c>
       <c r="U4">
         <v>0</v>
       </c>
       <c r="V4">
-        <v>0.12291000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0.12271</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1869,67 +1258,67 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>5.9389999999999998E-2</v>
+        <v>5.9229999999999998E-2</v>
       </c>
       <c r="D5">
-        <v>0.11319</v>
+        <v>0.11301</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.11323</v>
+        <v>0.11305</v>
       </c>
       <c r="G5">
-        <v>6.4500000000000002E-2</v>
+        <v>6.4280000000000004E-2</v>
       </c>
       <c r="H5">
-        <v>0.11892999999999999</v>
+        <v>0.11869</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0.11909</v>
+        <v>0.11885999999999999</v>
       </c>
       <c r="K5">
-        <v>6.4500000000000002E-2</v>
+        <v>6.4280000000000004E-2</v>
       </c>
       <c r="L5">
-        <v>0.11047999999999999</v>
+        <v>0.11022</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5">
+        <v>0.11024</v>
+      </c>
+      <c r="O5">
+        <v>6.012E-2</v>
+      </c>
+      <c r="P5">
+        <v>0.11869</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0.11905</v>
+      </c>
+      <c r="S5">
+        <v>6.012E-2</v>
+      </c>
+      <c r="T5">
+        <v>0.11022</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
         <v>0.1105</v>
       </c>
-      <c r="O5">
-        <v>6.0409999999999998E-2</v>
-      </c>
-      <c r="P5">
-        <v>0.11892999999999999</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0.11928999999999999</v>
-      </c>
-      <c r="S5">
-        <v>6.0409999999999998E-2</v>
-      </c>
-      <c r="T5">
-        <v>0.11047999999999999</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0.11075</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1937,67 +1326,67 @@
         <v>20</v>
       </c>
       <c r="C6">
-        <v>5.0049999999999997E-2</v>
+        <v>4.9910000000000003E-2</v>
       </c>
       <c r="D6">
-        <v>9.5060000000000006E-2</v>
+        <v>9.4790000000000013E-2</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>9.5150000000000012E-2</v>
+        <v>9.4879999999999992E-2</v>
       </c>
       <c r="G6">
-        <v>5.4369999999999988E-2</v>
+        <v>5.4140000000000001E-2</v>
       </c>
       <c r="H6">
-        <v>9.9890000000000007E-2</v>
+        <v>9.9510000000000001E-2</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>9.9930000000000005E-2</v>
+        <v>9.955E-2</v>
       </c>
       <c r="K6">
-        <v>5.4369999999999988E-2</v>
+        <v>5.4140000000000001E-2</v>
       </c>
       <c r="L6">
-        <v>9.2769999999999991E-2</v>
+        <v>9.2450000000000004E-2</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
-        <v>9.282E-2</v>
+        <v>9.2499999999999999E-2</v>
       </c>
       <c r="O6">
-        <v>5.0689999999999999E-2</v>
+        <v>5.0380000000000001E-2</v>
       </c>
       <c r="P6">
-        <v>9.9890000000000007E-2</v>
+        <v>9.9510000000000001E-2</v>
       </c>
       <c r="Q6">
         <v>0</v>
       </c>
       <c r="R6">
-        <v>0.10031</v>
+        <v>9.9919999999999995E-2</v>
       </c>
       <c r="S6">
-        <v>5.0689999999999999E-2</v>
+        <v>5.0380000000000001E-2</v>
       </c>
       <c r="T6">
-        <v>9.2769999999999991E-2</v>
+        <v>9.2450000000000004E-2</v>
       </c>
       <c r="U6">
         <v>0</v>
       </c>
       <c r="V6">
-        <v>9.3120000000000008E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+        <v>9.2799999999999994E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -2005,67 +1394,67 @@
         <v>25</v>
       </c>
       <c r="C7">
-        <v>5.1060000000000001E-2</v>
+        <v>5.0889999999999998E-2</v>
       </c>
       <c r="D7">
-        <v>7.7900000000000011E-2</v>
+        <v>7.7719999999999997E-2</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>7.7969999999999998E-2</v>
+        <v>7.7790000000000012E-2</v>
       </c>
       <c r="G7">
-        <v>5.4820000000000001E-2</v>
+        <v>5.4609999999999999E-2</v>
       </c>
       <c r="H7">
-        <v>8.2049999999999998E-2</v>
+        <v>8.181999999999999E-2</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>8.2170000000000007E-2</v>
+        <v>8.1939999999999999E-2</v>
       </c>
       <c r="K7">
-        <v>5.4820000000000001E-2</v>
+        <v>5.4609999999999999E-2</v>
       </c>
       <c r="L7">
-        <v>7.6109999999999997E-2</v>
+        <v>7.5870000000000007E-2</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
       <c r="N7">
-        <v>7.6200000000000004E-2</v>
+        <v>7.5950000000000004E-2</v>
       </c>
       <c r="O7">
-        <v>5.1580000000000001E-2</v>
+        <v>5.1290000000000002E-2</v>
       </c>
       <c r="P7">
-        <v>8.2049999999999998E-2</v>
+        <v>8.181999999999999E-2</v>
       </c>
       <c r="Q7">
         <v>0</v>
       </c>
       <c r="R7">
-        <v>8.2430000000000003E-2</v>
+        <v>8.2189999999999999E-2</v>
       </c>
       <c r="S7">
-        <v>5.1580000000000001E-2</v>
+        <v>5.1290000000000002E-2</v>
       </c>
       <c r="T7">
-        <v>7.6109999999999997E-2</v>
+        <v>7.5870000000000007E-2</v>
       </c>
       <c r="U7">
         <v>0</v>
       </c>
       <c r="V7">
-        <v>7.6469999999999996E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+        <v>7.6239999999999988E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -2073,67 +1462,67 @@
         <v>30</v>
       </c>
       <c r="C8">
-        <v>5.0200000000000002E-2</v>
+        <v>5.0099999999999999E-2</v>
       </c>
       <c r="D8">
-        <v>7.8060000000000004E-2</v>
+        <v>7.7930000000000013E-2</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>7.8090000000000007E-2</v>
+        <v>7.7959999999999988E-2</v>
       </c>
       <c r="G8">
-        <v>5.3469999999999997E-2</v>
+        <v>5.33E-2</v>
       </c>
       <c r="H8">
-        <v>8.2180000000000003E-2</v>
+        <v>8.2019999999999996E-2</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>8.233E-2</v>
+        <v>8.2170000000000007E-2</v>
       </c>
       <c r="K8">
-        <v>5.3469999999999997E-2</v>
+        <v>5.33E-2</v>
       </c>
       <c r="L8">
-        <v>7.5900000000000009E-2</v>
+        <v>7.5700000000000003E-2</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
       <c r="N8">
-        <v>7.5909999999999991E-2</v>
+        <v>7.571E-2</v>
       </c>
       <c r="O8">
-        <v>5.0540000000000002E-2</v>
+        <v>5.0349999999999999E-2</v>
       </c>
       <c r="P8">
-        <v>8.2180000000000003E-2</v>
+        <v>8.2019999999999996E-2</v>
       </c>
       <c r="Q8">
         <v>0</v>
       </c>
       <c r="R8">
-        <v>8.2450000000000009E-2</v>
+        <v>8.2290000000000002E-2</v>
       </c>
       <c r="S8">
-        <v>5.0540000000000002E-2</v>
+        <v>5.0349999999999999E-2</v>
       </c>
       <c r="T8">
-        <v>7.5900000000000009E-2</v>
+        <v>7.5700000000000003E-2</v>
       </c>
       <c r="U8">
         <v>0</v>
       </c>
       <c r="V8">
-        <v>7.6189999999999994E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+        <v>7.5989999999999988E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -2141,67 +1530,67 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>5.6390000000000003E-2</v>
+        <v>5.6300000000000003E-2</v>
       </c>
       <c r="D9">
-        <v>6.9739999999999996E-2</v>
+        <v>6.966E-2</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>7.1749999999999994E-2</v>
+        <v>7.1650000000000005E-2</v>
       </c>
       <c r="G9">
-        <v>5.9490000000000001E-2</v>
+        <v>5.9360000000000003E-2</v>
       </c>
       <c r="H9">
-        <v>7.331E-2</v>
+        <v>7.3209999999999997E-2</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>7.553E-2</v>
+        <v>7.5400000000000009E-2</v>
       </c>
       <c r="K9">
-        <v>5.9490000000000001E-2</v>
+        <v>5.9360000000000003E-2</v>
       </c>
       <c r="L9">
-        <v>6.8010000000000001E-2</v>
+        <v>6.7849999999999994E-2</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
       <c r="N9">
-        <v>7.2279999999999997E-2</v>
+        <v>7.2120000000000004E-2</v>
       </c>
       <c r="O9">
-        <v>5.6030000000000003E-2</v>
+        <v>5.5879999999999999E-2</v>
       </c>
       <c r="P9">
-        <v>7.331E-2</v>
+        <v>7.3209999999999997E-2</v>
       </c>
       <c r="Q9">
         <v>0</v>
       </c>
       <c r="R9">
-        <v>7.392E-2</v>
+        <v>7.3810000000000001E-2</v>
       </c>
       <c r="S9">
-        <v>5.6030000000000003E-2</v>
+        <v>5.5879999999999999E-2</v>
       </c>
       <c r="T9">
-        <v>6.8010000000000001E-2</v>
+        <v>6.7849999999999994E-2</v>
       </c>
       <c r="U9">
         <v>0</v>
       </c>
       <c r="V9">
-        <v>7.0489999999999997E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+        <v>7.0319999999999994E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -2209,67 +1598,67 @@
         <v>40</v>
       </c>
       <c r="C10">
-        <v>5.6180000000000001E-2</v>
+        <v>5.6090000000000001E-2</v>
       </c>
       <c r="D10">
-        <v>6.2080000000000003E-2</v>
+        <v>6.2020000000000013E-2</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>6.6989999999999994E-2</v>
+        <v>6.6909999999999997E-2</v>
       </c>
       <c r="G10">
-        <v>5.9270000000000003E-2</v>
+        <v>5.9159999999999997E-2</v>
       </c>
       <c r="H10">
-        <v>6.5759999999999999E-2</v>
+        <v>6.5680000000000002E-2</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>7.0830000000000004E-2</v>
+        <v>7.0730000000000001E-2</v>
       </c>
       <c r="K10">
-        <v>5.9270000000000003E-2</v>
+        <v>5.9159999999999997E-2</v>
       </c>
       <c r="L10">
-        <v>6.0089999999999998E-2</v>
+        <v>5.9990000000000002E-2</v>
       </c>
       <c r="M10">
         <v>0</v>
       </c>
       <c r="N10">
-        <v>6.7530000000000007E-2</v>
+        <v>6.7420000000000008E-2</v>
       </c>
       <c r="O10">
-        <v>5.5370000000000003E-2</v>
+        <v>5.5229999999999987E-2</v>
       </c>
       <c r="P10">
-        <v>6.5759999999999999E-2</v>
+        <v>6.5680000000000002E-2</v>
       </c>
       <c r="Q10">
         <v>0</v>
       </c>
       <c r="R10">
-        <v>6.8790000000000004E-2</v>
+        <v>6.8659999999999999E-2</v>
       </c>
       <c r="S10">
-        <v>5.5370000000000003E-2</v>
+        <v>5.5229999999999987E-2</v>
       </c>
       <c r="T10">
-        <v>6.0089999999999998E-2</v>
+        <v>5.9990000000000002E-2</v>
       </c>
       <c r="U10">
         <v>0</v>
       </c>
       <c r="V10">
-        <v>6.5379999999999994E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+        <v>6.5239999999999992E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -2277,64 +1666,64 @@
         <v>45</v>
       </c>
       <c r="C11">
-        <v>5.4179999999999999E-2</v>
+        <v>5.4090000000000013E-2</v>
       </c>
       <c r="D11">
-        <v>6.1969999999999997E-2</v>
+        <v>6.1940000000000002E-2</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>6.5849999999999992E-2</v>
+        <v>6.5790000000000001E-2</v>
       </c>
       <c r="G11">
-        <v>5.7000000000000002E-2</v>
+        <v>5.6919999999999998E-2</v>
       </c>
       <c r="H11">
-        <v>6.5420000000000006E-2</v>
+        <v>6.5370000000000011E-2</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>6.9419999999999996E-2</v>
+        <v>6.9339999999999999E-2</v>
       </c>
       <c r="K11">
-        <v>5.7000000000000002E-2</v>
+        <v>5.6919999999999998E-2</v>
       </c>
       <c r="L11">
-        <v>5.9950000000000003E-2</v>
+        <v>5.9889999999999999E-2</v>
       </c>
       <c r="M11">
         <v>0</v>
       </c>
       <c r="N11">
-        <v>6.6180000000000003E-2</v>
+        <v>6.6099999999999992E-2</v>
       </c>
       <c r="O11">
-        <v>5.3319999999999999E-2</v>
+        <v>5.3159999999999999E-2</v>
       </c>
       <c r="P11">
-        <v>6.5420000000000006E-2</v>
+        <v>6.5370000000000011E-2</v>
       </c>
       <c r="Q11">
         <v>0</v>
       </c>
       <c r="R11">
-        <v>6.7519999999999997E-2</v>
+        <v>6.7409999999999998E-2</v>
       </c>
       <c r="S11">
-        <v>5.3319999999999999E-2</v>
+        <v>5.3159999999999999E-2</v>
       </c>
       <c r="T11">
-        <v>5.9950000000000003E-2</v>
+        <v>5.9889999999999999E-2</v>
       </c>
       <c r="U11">
         <v>0</v>
       </c>
       <c r="V11">
-        <v>6.4189999999999997E-2</v>
+        <v>6.4069999999999988E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2345,72 +1734,72 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R46"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R26"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="D4" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
+      <c r="E4" t="s">
         <v>39</v>
       </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" t="s">
-        <v>35</v>
-      </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>0</v>
       </c>
@@ -2424,28 +1813,28 @@
         <v>0.22881801939514301</v>
       </c>
       <c r="E5">
-        <v>6.9900000000000004E-2</v>
+        <v>6.9769999999999999E-2</v>
       </c>
       <c r="F5">
-        <v>0.12667999999999999</v>
+        <v>0.1265</v>
       </c>
       <c r="G5">
-        <v>0.12712999999999999</v>
+        <v>0.12695000000000001</v>
       </c>
       <c r="H5">
-        <f>(E5-B5)/B5</f>
-        <v>-0.51665614759244183</v>
+        <f t="shared" ref="H5:H14" si="0">(E5-B5)/B5</f>
+        <v>-0.51755507035085357</v>
       </c>
       <c r="I5">
-        <f t="shared" ref="I5:J14" si="0">(F5-C5)/C5</f>
-        <v>-0.4350428094527104</v>
+        <f t="shared" ref="I5:I14" si="1">(F5-C5)/C5</f>
+        <v>-0.43584555885512988</v>
       </c>
       <c r="J5">
-        <f t="shared" si="0"/>
-        <v>-0.44440564455520104</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" ref="J5:J14" si="2">(G5-D5)/D5</f>
+        <v>-0.44519229588832504</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>8.7266462599716502E-2</v>
       </c>
@@ -2459,28 +1848,28 @@
         <v>0.242018594909096</v>
       </c>
       <c r="E6">
-        <v>7.0080000000000003E-2</v>
+        <v>6.9930000000000006E-2</v>
       </c>
       <c r="F6">
-        <v>0.14549000000000001</v>
+        <v>0.14530999999999999</v>
       </c>
       <c r="G6">
-        <v>0.14571999999999999</v>
+        <v>0.14552999999999999</v>
       </c>
       <c r="H6">
-        <f t="shared" ref="H6:H14" si="1">(E6-B6)/B6</f>
-        <v>-0.5191563189155165</v>
+        <f t="shared" si="0"/>
+        <v>-0.52018552200002954</v>
       </c>
       <c r="I6">
-        <f t="shared" si="0"/>
-        <v>-0.39103827835940974</v>
+        <f t="shared" si="1"/>
+        <v>-0.39179168484710863</v>
       </c>
       <c r="J6">
-        <f t="shared" si="0"/>
-        <v>-0.39789750430237181</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>-0.39868256794622681</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>0.174532925199433</v>
       </c>
@@ -2494,28 +1883,28 @@
         <v>0.19790102555998401</v>
       </c>
       <c r="E7">
-        <v>5.9830000000000001E-2</v>
+        <v>5.9639999999999999E-2</v>
       </c>
       <c r="F7">
-        <v>0.13292999999999999</v>
+        <v>0.13275000000000001</v>
       </c>
       <c r="G7">
-        <v>0.13317999999999999</v>
+        <v>0.13299</v>
       </c>
       <c r="H7">
+        <f t="shared" si="0"/>
+        <v>-0.51598106445055814</v>
+      </c>
+      <c r="I7">
         <f t="shared" si="1"/>
-        <v>-0.51443908595031673</v>
-      </c>
-      <c r="I7">
-        <f t="shared" si="0"/>
-        <v>-0.32022647930355336</v>
+        <v>-0.32114695800456405</v>
       </c>
       <c r="J7">
-        <f t="shared" si="0"/>
-        <v>-0.3270373429185035</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>-0.32799741879209926</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>0.26179938779914902</v>
       </c>
@@ -2529,28 +1918,28 @@
         <v>0.201287478382664</v>
       </c>
       <c r="E8">
-        <v>6.4500000000000002E-2</v>
+        <v>6.4280000000000004E-2</v>
       </c>
       <c r="F8">
-        <v>0.11892999999999999</v>
+        <v>0.11869</v>
       </c>
       <c r="G8">
-        <v>0.11909</v>
+        <v>0.11885999999999999</v>
       </c>
       <c r="H8">
+        <f t="shared" si="0"/>
+        <v>-0.46069723197752499</v>
+      </c>
+      <c r="I8">
         <f t="shared" si="1"/>
-        <v>-0.45885145399113819</v>
-      </c>
-      <c r="I8">
-        <f t="shared" si="0"/>
-        <v>-0.40525002865747578</v>
+        <v>-0.40645023039902289</v>
       </c>
       <c r="J8">
-        <f t="shared" si="0"/>
-        <v>-0.40835862738764034</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>-0.40950127173813872</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>0.34906585039886601</v>
       </c>
@@ -2564,28 +1953,28 @@
         <v>0.150365553159441</v>
       </c>
       <c r="E9">
-        <v>5.4369999999999988E-2</v>
+        <v>5.4140000000000001E-2</v>
       </c>
       <c r="F9">
-        <v>9.9890000000000007E-2</v>
+        <v>9.9510000000000001E-2</v>
       </c>
       <c r="G9">
-        <v>9.9930000000000005E-2</v>
+        <v>9.955E-2</v>
       </c>
       <c r="H9">
+        <f t="shared" si="0"/>
+        <v>-0.48799207422154595</v>
+      </c>
+      <c r="I9">
         <f t="shared" si="1"/>
-        <v>-0.48581693896242079</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="0"/>
-        <v>-0.32153483200117799</v>
+        <v>-0.32411583874699396</v>
       </c>
       <c r="J9">
-        <f t="shared" si="0"/>
-        <v>-0.33541959644148922</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>-0.33794677099720061</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>0.43633231299858199</v>
       </c>
@@ -2599,28 +1988,28 @@
         <v>0.129943884511105</v>
       </c>
       <c r="E10">
-        <v>5.4820000000000001E-2</v>
+        <v>5.4609999999999999E-2</v>
       </c>
       <c r="F10">
-        <v>8.2049999999999998E-2</v>
+        <v>8.181999999999999E-2</v>
       </c>
       <c r="G10">
-        <v>8.2170000000000007E-2</v>
+        <v>8.1939999999999999E-2</v>
       </c>
       <c r="H10">
+        <f t="shared" si="0"/>
+        <v>-0.51737200141170658</v>
+      </c>
+      <c r="I10">
         <f t="shared" si="1"/>
-        <v>-0.5155160797910594</v>
-      </c>
-      <c r="I10">
-        <f t="shared" si="0"/>
-        <v>-0.29591522896168171</v>
+        <v>-0.29788889742406832</v>
       </c>
       <c r="J10">
-        <f t="shared" si="0"/>
-        <v>-0.36765011828642263</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>-0.36942011308737344</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>0.52359877559829904</v>
       </c>
@@ -2634,28 +2023,28 @@
         <v>0.13194455836051999</v>
       </c>
       <c r="E11">
-        <v>5.3469999999999997E-2</v>
+        <v>5.33E-2</v>
       </c>
       <c r="F11">
-        <v>8.2180000000000003E-2</v>
+        <v>8.2019999999999996E-2</v>
       </c>
       <c r="G11">
-        <v>8.233E-2</v>
+        <v>8.2170000000000007E-2</v>
       </c>
       <c r="H11">
+        <f t="shared" si="0"/>
+        <v>-0.49146951146930323</v>
+      </c>
+      <c r="I11">
         <f t="shared" si="1"/>
-        <v>-0.489847556815453</v>
-      </c>
-      <c r="I11">
-        <f t="shared" si="0"/>
-        <v>-0.3546638900145368</v>
+        <v>-0.3559203243975701</v>
       </c>
       <c r="J11">
-        <f t="shared" si="0"/>
-        <v>-0.37602580187471751</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>-0.37723843240672333</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>0.61086523819801497</v>
       </c>
@@ -2669,28 +2058,28 @@
         <v>0.12722112864763599</v>
       </c>
       <c r="E12">
-        <v>5.9490000000000001E-2</v>
+        <v>5.9360000000000003E-2</v>
       </c>
       <c r="F12">
-        <v>7.331E-2</v>
+        <v>7.3209999999999997E-2</v>
       </c>
       <c r="G12">
-        <v>7.553E-2</v>
+        <v>7.5400000000000009E-2</v>
       </c>
       <c r="H12">
+        <f t="shared" si="0"/>
+        <v>-0.46254553638429735</v>
+      </c>
+      <c r="I12">
         <f t="shared" si="1"/>
-        <v>-0.46136849662233576</v>
-      </c>
-      <c r="I12">
-        <f t="shared" si="0"/>
-        <v>-0.35926632652043422</v>
+        <v>-0.36014033234976117</v>
       </c>
       <c r="J12">
-        <f t="shared" si="0"/>
-        <v>-0.40630930724411957</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>-0.40733115008879395</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>0.69813170079773201</v>
       </c>
@@ -2704,28 +2093,28 @@
         <v>0.112717366536148</v>
       </c>
       <c r="E13">
-        <v>5.9270000000000003E-2</v>
+        <v>5.9159999999999997E-2</v>
       </c>
       <c r="F13">
-        <v>6.5759999999999999E-2</v>
+        <v>6.5680000000000002E-2</v>
       </c>
       <c r="G13">
-        <v>7.0830000000000004E-2</v>
+        <v>7.0730000000000001E-2</v>
       </c>
       <c r="H13">
+        <f t="shared" si="0"/>
+        <v>-0.42424750200043104</v>
+      </c>
+      <c r="I13">
         <f t="shared" si="1"/>
-        <v>-0.42317696828204099</v>
-      </c>
-      <c r="I13">
-        <f t="shared" si="0"/>
-        <v>-0.31787348850288599</v>
+        <v>-0.31870332610811358</v>
       </c>
       <c r="J13">
-        <f t="shared" si="0"/>
-        <v>-0.37161413385855574</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>-0.37250130859544894</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>0.78539816339744795</v>
       </c>
@@ -2739,28 +2128,28 @@
         <v>0.115269005057364</v>
       </c>
       <c r="E14">
-        <v>5.7000000000000002E-2</v>
+        <v>5.6919999999999998E-2</v>
       </c>
       <c r="F14">
-        <v>6.5420000000000006E-2</v>
+        <v>6.5370000000000011E-2</v>
       </c>
       <c r="G14">
-        <v>6.9419999999999996E-2</v>
+        <v>6.9339999999999999E-2</v>
       </c>
       <c r="H14">
+        <f t="shared" si="0"/>
+        <v>-0.41472639219684254</v>
+      </c>
+      <c r="I14">
         <f t="shared" si="1"/>
-        <v>-0.41390380104040797</v>
-      </c>
-      <c r="I14">
-        <f t="shared" si="0"/>
-        <v>-0.38465051645864612</v>
+        <v>-0.38512082330941139</v>
       </c>
       <c r="J14">
-        <f t="shared" si="0"/>
-        <v>-0.39775657848826834</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>-0.39845060720795916</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>0.87266462599716499</v>
       </c>
@@ -2777,7 +2166,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>0.95993108859688103</v>
       </c>
@@ -2791,7 +2180,7 @@
         <v>0.12722112864763599</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>1.0471975511966001</v>
       </c>
@@ -2805,7 +2194,7 @@
         <v>0.13194455836051999</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>1.13446401379631</v>
       </c>
@@ -2819,7 +2208,7 @@
         <v>0.129943884511105</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>1.2217304763960299</v>
       </c>
@@ -2833,7 +2222,7 @@
         <v>0.150365553159441</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>1.3089969389957501</v>
       </c>
@@ -2847,7 +2236,7 @@
         <v>0.201287478382664</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>1.39626340159546</v>
       </c>
@@ -2861,7 +2250,7 @@
         <v>0.19790102555998401</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>1.48352986419518</v>
       </c>
@@ -2875,7 +2264,7 @@
         <v>0.242018594909096</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>1.5707963267949001</v>
       </c>
@@ -2889,340 +2278,29 @@
         <v>0.22881801939514301</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" t="s">
-        <v>36</v>
-      </c>
-      <c r="D27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E27" t="s">
-        <v>35</v>
-      </c>
-      <c r="F27" t="s">
-        <v>36</v>
-      </c>
-      <c r="G27" t="s">
-        <v>37</v>
-      </c>
-      <c r="H27" t="s">
-        <v>35</v>
-      </c>
-      <c r="I27" t="s">
-        <v>36</v>
-      </c>
-      <c r="J27" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>0</v>
-      </c>
-      <c r="B28">
-        <v>0.132232093010343</v>
-      </c>
-      <c r="C28">
-        <v>9.55218933923834E-2</v>
-      </c>
-      <c r="D28">
-        <v>0.13761963661118301</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>8.7266462599716502E-2</v>
-      </c>
-      <c r="B29">
-        <v>0.121683867827998</v>
-      </c>
-      <c r="C29">
-        <v>9.7854450654004096E-2</v>
-      </c>
-      <c r="D29">
-        <v>0.12609626859930301</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>0.174532925199433</v>
-      </c>
-      <c r="B30">
-        <v>0.129469308427685</v>
-      </c>
-      <c r="C30">
-        <v>9.8119679775397803E-2</v>
-      </c>
-      <c r="D30">
-        <v>0.13483157857154501</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>0.26179938779914902</v>
-      </c>
-      <c r="B31">
-        <v>0.119927643302493</v>
-      </c>
-      <c r="C31">
-        <v>9.0768804749441906E-2</v>
-      </c>
-      <c r="D31">
-        <v>0.12538389305328401</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>0.34906585039886601</v>
-      </c>
-      <c r="B32">
-        <v>0.12460646127702101</v>
-      </c>
-      <c r="C32">
-        <v>9.2318128174672498E-2</v>
-      </c>
-      <c r="D32">
-        <v>0.129277040440688</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>0.43633231299858199</v>
-      </c>
-      <c r="B33">
-        <v>0.10421169672170701</v>
-      </c>
-      <c r="C33">
-        <v>7.1819293069161197E-2</v>
-      </c>
-      <c r="D33">
-        <v>0.10787189330256899</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>0.52359877559829904</v>
-      </c>
-      <c r="B34">
-        <v>9.6632270745634199E-2</v>
-      </c>
-      <c r="C34">
-        <v>6.6401016719959002E-2</v>
-      </c>
-      <c r="D34">
-        <v>9.9507069318539795E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>0.61086523819801497</v>
-      </c>
-      <c r="B35">
-        <v>9.6736047866732594E-2</v>
-      </c>
-      <c r="C35">
-        <v>5.8162268453324902E-2</v>
-      </c>
-      <c r="D35">
-        <v>9.8793606866758601E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>0.69813170079773201</v>
-      </c>
-      <c r="B36">
-        <v>8.3372399593321905E-2</v>
-      </c>
-      <c r="C36">
-        <v>5.6316041155931799E-2</v>
-      </c>
-      <c r="D36">
-        <v>8.6108603940658196E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>0.78539816339744795</v>
-      </c>
-      <c r="B37">
-        <v>8.2268565543065303E-2</v>
-      </c>
-      <c r="C37">
-        <v>4.9343469269231603E-2</v>
-      </c>
-      <c r="D37">
-        <v>8.4053221025017902E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>0.87266462599716499</v>
-      </c>
-      <c r="B38">
-        <v>8.3951696198669795E-2</v>
-      </c>
-      <c r="C38">
-        <v>5.5538905512266097E-2</v>
-      </c>
-      <c r="D38">
-        <v>8.6621156724383502E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>0.95993108859688103</v>
-      </c>
-      <c r="B39">
-        <v>8.8765075961770606E-2</v>
-      </c>
-      <c r="C39">
-        <v>4.7363951673053101E-2</v>
-      </c>
-      <c r="D39">
-        <v>9.0717791779035703E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>1.0471975511966001</v>
-      </c>
-      <c r="B40">
-        <v>8.8701157679209094E-2</v>
-      </c>
-      <c r="C40">
-        <v>5.1556793900650502E-2</v>
-      </c>
-      <c r="D40">
-        <v>9.1220534195848496E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>1.13446401379631</v>
-      </c>
-      <c r="B41">
-        <v>0.108524896941606</v>
-      </c>
-      <c r="C41">
-        <v>5.36945862049392E-2</v>
-      </c>
-      <c r="D41">
-        <v>0.11130197776297</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>1.2217304763960299</v>
-      </c>
-      <c r="B42">
-        <v>0.102688187664027</v>
-      </c>
-      <c r="C42">
-        <v>5.3583072787593902E-2</v>
-      </c>
-      <c r="D42">
-        <v>0.107157215727303</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>1.3089969389957501</v>
-      </c>
-      <c r="B43">
-        <v>0.11732321240533999</v>
-      </c>
-      <c r="C43">
-        <v>5.9746398875489097E-2</v>
-      </c>
-      <c r="D43">
-        <v>0.122005851455536</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>1.39626340159546</v>
-      </c>
-      <c r="B44">
-        <v>0.128849013038245</v>
-      </c>
-      <c r="C44">
-        <v>6.9169681595875401E-2</v>
-      </c>
-      <c r="D44">
-        <v>0.135388114051613</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>1.48352986419518</v>
-      </c>
-      <c r="B45">
-        <v>0.17299767164900101</v>
-      </c>
-      <c r="C45">
-        <v>7.93314091368892E-2</v>
-      </c>
-      <c r="D45">
-        <v>0.182908397947733</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>1.5707963267949001</v>
-      </c>
-      <c r="B46">
-        <v>0.164968138604421</v>
-      </c>
-      <c r="C46">
-        <v>8.60993664443582E-2</v>
-      </c>
-      <c r="D46">
-        <v>0.17574628724542399</v>
-      </c>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B26" s="2"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="E26:G26"/>
+    <mergeCell ref="E3:G3"/>
     <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>